--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-06-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C888B-FEDD-459D-9F4D-E6E3E0DFC0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8833B4-D35F-41F0-8809-42503BD0A74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="3660" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41325" yWindow="3150" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -883,9 +883,6 @@
     <t>£67.92</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/725mm-celotex-pl4060-pir-insulated-plasterboard-12m-x-24m/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.onlineinsulation-sales.com', port=443) at 0x1d500b50f10&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
-  </si>
-  <si>
     <t>£81.97</t>
   </si>
   <si>
@@ -1214,6 +1211,9 @@
   </si>
   <si>
     <t>£2655.52</t>
+  </si>
+  <si>
+    <t>£62.55</t>
   </si>
 </sst>
 </file>
@@ -1676,7 +1676,7 @@
         <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O3" t="s">
         <v>43</v>
@@ -1788,7 +1788,7 @@
         <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O4" t="s">
         <v>57</v>
@@ -1844,7 +1844,7 @@
         <v>69</v>
       </c>
       <c r="N5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O5" t="s">
         <v>70</v>
@@ -1900,7 +1900,7 @@
         <v>83</v>
       </c>
       <c r="N6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O6" t="s">
         <v>84</v>
@@ -1956,7 +1956,7 @@
         <v>97</v>
       </c>
       <c r="N7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O7" t="s">
         <v>98</v>
@@ -2012,7 +2012,7 @@
         <v>108</v>
       </c>
       <c r="N8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O8" t="s">
         <v>98</v>
@@ -2068,7 +2068,7 @@
         <v>119</v>
       </c>
       <c r="N9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O9" t="s">
         <v>120</v>
@@ -2124,7 +2124,7 @@
         <v>133</v>
       </c>
       <c r="N10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O10" t="s">
         <v>134</v>
@@ -2180,7 +2180,7 @@
         <v>146</v>
       </c>
       <c r="N11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O11" t="s">
         <v>147</v>
@@ -2236,7 +2236,7 @@
         <v>160</v>
       </c>
       <c r="N12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O12" t="s">
         <v>161</v>
@@ -2292,7 +2292,7 @@
         <v>173</v>
       </c>
       <c r="N13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O13" t="s">
         <v>174</v>
@@ -2348,7 +2348,7 @@
         <v>187</v>
       </c>
       <c r="N14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O14" t="s">
         <v>188</v>
@@ -2460,7 +2460,7 @@
         <v>213</v>
       </c>
       <c r="N16" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O16" t="s">
         <v>214</v>
@@ -2516,7 +2516,7 @@
         <v>225</v>
       </c>
       <c r="N17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O17" t="s">
         <v>226</v>
@@ -2572,7 +2572,7 @@
         <v>238</v>
       </c>
       <c r="N18" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O18" t="s">
         <v>239</v>
@@ -2628,7 +2628,7 @@
         <v>252</v>
       </c>
       <c r="N19" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O19" t="s">
         <v>253</v>
@@ -2684,7 +2684,7 @@
         <v>264</v>
       </c>
       <c r="N20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O20" t="s">
         <v>265</v>
@@ -2740,7 +2740,7 @@
         <v>277</v>
       </c>
       <c r="N21" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O21" t="s">
         <v>278</v>
@@ -2778,166 +2778,166 @@
         <v>286</v>
       </c>
       <c r="H22" t="s">
+        <v>397</v>
+      </c>
+      <c r="I22" t="s">
         <v>287</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>288</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>289</v>
-      </c>
-      <c r="K22" t="s">
-        <v>290</v>
       </c>
       <c r="L22" t="s">
         <v>27</v>
       </c>
       <c r="M22" t="s">
+        <v>290</v>
+      </c>
+      <c r="N22" t="s">
+        <v>390</v>
+      </c>
+      <c r="O22" t="s">
         <v>291</v>
       </c>
-      <c r="N22" t="s">
-        <v>391</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>292</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>293</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>294</v>
-      </c>
-      <c r="R22" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" t="s">
         <v>296</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>297</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" t="s">
+        <v>297</v>
+      </c>
+      <c r="F23" t="s">
         <v>298</v>
-      </c>
-      <c r="D23" t="s">
-        <v>298</v>
-      </c>
-      <c r="E23" t="s">
-        <v>298</v>
-      </c>
-      <c r="F23" t="s">
-        <v>299</v>
       </c>
       <c r="G23" t="s">
         <v>156</v>
       </c>
       <c r="H23" t="s">
+        <v>299</v>
+      </c>
+      <c r="I23" t="s">
         <v>300</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>301</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>302</v>
-      </c>
-      <c r="K23" t="s">
-        <v>303</v>
       </c>
       <c r="L23" t="s">
         <v>27</v>
       </c>
       <c r="M23" t="s">
+        <v>303</v>
+      </c>
+      <c r="N23" t="s">
+        <v>391</v>
+      </c>
+      <c r="O23" t="s">
         <v>304</v>
       </c>
-      <c r="N23" t="s">
-        <v>392</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>305</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>306</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>307</v>
-      </c>
-      <c r="R23" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>308</v>
+      </c>
+      <c r="B24" t="s">
         <v>309</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>310</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>310</v>
+      </c>
+      <c r="E24" t="s">
+        <v>310</v>
+      </c>
+      <c r="F24" t="s">
         <v>311</v>
-      </c>
-      <c r="D24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F24" t="s">
-        <v>312</v>
       </c>
       <c r="G24" t="s">
         <v>156</v>
       </c>
       <c r="H24" t="s">
+        <v>312</v>
+      </c>
+      <c r="I24" t="s">
         <v>313</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>314</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>315</v>
-      </c>
-      <c r="K24" t="s">
-        <v>316</v>
       </c>
       <c r="L24" t="s">
         <v>27</v>
       </c>
       <c r="M24" t="s">
+        <v>316</v>
+      </c>
+      <c r="N24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O24" t="s">
         <v>317</v>
       </c>
-      <c r="N24" t="s">
-        <v>393</v>
-      </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>318</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>319</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>320</v>
-      </c>
-      <c r="R24" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" t="s">
         <v>322</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>323</v>
       </c>
-      <c r="C25" t="s">
-        <v>324</v>
-      </c>
       <c r="D25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F25" t="s">
         <v>156</v>
@@ -2952,7 +2952,7 @@
         <v>156</v>
       </c>
       <c r="J25" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K25" t="s">
         <v>156</v>
@@ -2961,13 +2961,13 @@
         <v>156</v>
       </c>
       <c r="M25" t="s">
+        <v>325</v>
+      </c>
+      <c r="N25" t="s">
         <v>326</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>327</v>
-      </c>
-      <c r="O25" t="s">
-        <v>328</v>
       </c>
       <c r="P25" t="s">
         <v>156</v>
@@ -2981,226 +2981,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" t="s">
         <v>329</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>330</v>
       </c>
-      <c r="C26" t="s">
-        <v>331</v>
-      </c>
       <c r="D26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F26" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G26" t="s">
         <v>156</v>
       </c>
       <c r="H26" t="s">
+        <v>331</v>
+      </c>
+      <c r="I26" t="s">
         <v>332</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>333</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>334</v>
-      </c>
-      <c r="K26" t="s">
-        <v>335</v>
       </c>
       <c r="L26" t="s">
         <v>27</v>
       </c>
       <c r="M26" t="s">
+        <v>335</v>
+      </c>
+      <c r="N26" t="s">
+        <v>393</v>
+      </c>
+      <c r="O26" t="s">
         <v>336</v>
       </c>
-      <c r="N26" t="s">
-        <v>394</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>337</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>338</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>339</v>
-      </c>
-      <c r="R26" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>340</v>
+      </c>
+      <c r="B27" t="s">
         <v>341</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>342</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>342</v>
+      </c>
+      <c r="E27" t="s">
+        <v>342</v>
+      </c>
+      <c r="F27" t="s">
         <v>343</v>
-      </c>
-      <c r="D27" t="s">
-        <v>343</v>
-      </c>
-      <c r="E27" t="s">
-        <v>343</v>
-      </c>
-      <c r="F27" t="s">
-        <v>344</v>
       </c>
       <c r="G27" t="s">
         <v>156</v>
       </c>
       <c r="H27" t="s">
+        <v>344</v>
+      </c>
+      <c r="I27" t="s">
         <v>345</v>
-      </c>
-      <c r="I27" t="s">
-        <v>346</v>
       </c>
       <c r="J27" t="s">
         <v>156</v>
       </c>
       <c r="K27" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L27" t="s">
         <v>27</v>
       </c>
       <c r="M27" t="s">
+        <v>347</v>
+      </c>
+      <c r="N27" t="s">
+        <v>394</v>
+      </c>
+      <c r="O27" t="s">
         <v>348</v>
       </c>
-      <c r="N27" t="s">
-        <v>395</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q27" t="s">
         <v>349</v>
       </c>
-      <c r="P27" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>350</v>
-      </c>
-      <c r="R27" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>351</v>
+      </c>
+      <c r="B28" t="s">
         <v>352</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>353</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>353</v>
+      </c>
+      <c r="E28" t="s">
+        <v>353</v>
+      </c>
+      <c r="F28" t="s">
         <v>354</v>
-      </c>
-      <c r="D28" t="s">
-        <v>354</v>
-      </c>
-      <c r="E28" t="s">
-        <v>354</v>
-      </c>
-      <c r="F28" t="s">
-        <v>355</v>
       </c>
       <c r="G28" t="s">
         <v>156</v>
       </c>
       <c r="H28" t="s">
+        <v>355</v>
+      </c>
+      <c r="I28" t="s">
         <v>356</v>
-      </c>
-      <c r="I28" t="s">
-        <v>357</v>
       </c>
       <c r="J28" t="s">
         <v>156</v>
       </c>
       <c r="K28" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L28" t="s">
         <v>27</v>
       </c>
       <c r="M28" t="s">
+        <v>358</v>
+      </c>
+      <c r="N28" t="s">
+        <v>395</v>
+      </c>
+      <c r="O28" t="s">
         <v>359</v>
       </c>
-      <c r="N28" t="s">
-        <v>396</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>360</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>361</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>362</v>
-      </c>
-      <c r="R28" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>363</v>
+      </c>
+      <c r="B29" t="s">
         <v>364</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>365</v>
       </c>
-      <c r="C29" t="s">
-        <v>366</v>
-      </c>
       <c r="D29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G29" t="s">
         <v>156</v>
       </c>
       <c r="H29" t="s">
+        <v>366</v>
+      </c>
+      <c r="I29" t="s">
         <v>367</v>
-      </c>
-      <c r="I29" t="s">
-        <v>368</v>
       </c>
       <c r="J29" t="s">
         <v>156</v>
       </c>
       <c r="K29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L29" t="s">
         <v>156</v>
       </c>
       <c r="M29" t="s">
+        <v>369</v>
+      </c>
+      <c r="N29" t="s">
+        <v>396</v>
+      </c>
+      <c r="O29" t="s">
         <v>370</v>
       </c>
-      <c r="N29" t="s">
-        <v>397</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>371</v>
-      </c>
-      <c r="P29" t="s">
-        <v>372</v>
       </c>
       <c r="Q29" t="s">
         <v>156</v>
       </c>
       <c r="R29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
